--- a/packages/calculators/src/modules/test/4.5-pigs-manure/4.5-pigs-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.5-pigs-manure/4.5-pigs-manure.xlsx
@@ -1,21 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/4.5-pigs-manure/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D22E262-90C3-6E40-B5C9-665FAB9D5F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F8414B-A580-594F-8171-59E3C0E4A085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33040" yWindow="-1120" windowWidth="28800" windowHeight="15900" xr2:uid="{498306D6-A158-0A47-8C6F-02750C53E536}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{498306D6-A158-0A47-8C6F-02750C53E536}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
     <sheet name="4.5" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1028,6 +1026,31 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1962,8 +1985,8 @@
         <v>71</v>
       </c>
       <c r="B23">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
       <c r="D23" t="s">
         <v>79</v>
@@ -4010,7 +4033,7 @@
       </c>
       <c r="EA11">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB11" s="18">
         <f>DI11*DU11*$EA11</f>
@@ -4018,7 +4041,7 @@
       </c>
       <c r="EC11" s="18">
         <f t="shared" ref="EC11:EG11" si="6">DJ11*DV11*$EA11</f>
-        <v>1.0531124999999999</v>
+        <v>1.0521551250000001</v>
       </c>
       <c r="ED11" s="18">
         <f t="shared" si="6"/>
@@ -4090,7 +4113,7 @@
       </c>
       <c r="EU11">
         <f>EP11*DZ11*$EA11</f>
-        <v>0.16744488750000003</v>
+        <v>0.16729266487500002</v>
       </c>
       <c r="EV11">
         <f>EQ11*0*$EA11</f>
@@ -4098,11 +4121,11 @@
       </c>
       <c r="EW11" s="18">
         <f>SUM(EB11:EG11,ER11:EV11)/1000</f>
-        <v>1.2205573874999999E-3</v>
+        <v>1.2194477898750001E-3</v>
       </c>
       <c r="EX11">
         <f>SUM(EW11:EW14)</f>
-        <v>0.18582584679214284</v>
+        <v>0.18565691420414998</v>
       </c>
       <c r="EY11" s="18">
         <f>DI11*DO11</f>
@@ -4158,11 +4181,11 @@
       </c>
       <c r="FL11">
         <f>(EA11*FJ11*FK11)/1000</f>
-        <v>2.8740756515624999E-3</v>
+        <v>2.8714628555156253E-3</v>
       </c>
       <c r="FM11">
         <f>SUM(FL11:FL14)</f>
-        <v>3.5391171110624994E-2</v>
+        <v>3.5358997318706252E-2</v>
       </c>
       <c r="FN11" s="18">
         <f>Constants!$B$24</f>
@@ -4554,7 +4577,7 @@
       </c>
       <c r="EA12">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB12">
         <f t="shared" ref="EB12:EB15" si="35">DI12*DU12*$EA12</f>
@@ -4562,7 +4585,7 @@
       </c>
       <c r="EC12">
         <f t="shared" ref="EC12:EC15" si="36">DJ12*DV12*$EA12</f>
-        <v>2.2008524999999999</v>
+        <v>2.1988517249999999</v>
       </c>
       <c r="ED12">
         <f t="shared" ref="ED12:ED15" si="37">DK12*DW12*$EA12</f>
@@ -4634,7 +4657,7 @@
       </c>
       <c r="EU12">
         <f t="shared" ref="EU12:EU15" si="54">EP12*DZ12*$EA12</f>
-        <v>0.3499355475</v>
+        <v>0.34961742427500003</v>
       </c>
       <c r="EV12">
         <f t="shared" ref="EV12:EV15" si="55">EQ12*0*$EA12</f>
@@ -4642,7 +4665,7 @@
       </c>
       <c r="EW12">
         <f t="shared" ref="EW12:EW26" si="56">SUM(EB12:EG12,ER12:EV12)/1000</f>
-        <v>2.5507880474999996E-3</v>
+        <v>2.5484691492749997E-3</v>
       </c>
       <c r="EY12">
         <f t="shared" ref="EY12:EY15" si="57">DI12*DO12</f>
@@ -4698,7 +4721,7 @@
       </c>
       <c r="FL12">
         <f t="shared" ref="FL12:FL26" si="69">(EA12*FJ12*FK12)/1000</f>
-        <v>6.0064015790624991E-3</v>
+        <v>6.0009412139906239E-3</v>
       </c>
       <c r="FN12">
         <f>Constants!$B$24</f>
@@ -5077,7 +5100,7 @@
       </c>
       <c r="EA13">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB13">
         <f t="shared" si="35"/>
@@ -5097,7 +5120,7 @@
       </c>
       <c r="EF13">
         <f t="shared" si="39"/>
-        <v>48.142285714285713</v>
+        <v>48.098520000000001</v>
       </c>
       <c r="EG13">
         <f t="shared" si="40"/>
@@ -5149,7 +5172,7 @@
       </c>
       <c r="ES13">
         <f t="shared" si="52"/>
-        <v>20.821538571428569</v>
+        <v>20.8026099</v>
       </c>
       <c r="ET13">
         <f t="shared" si="53"/>
@@ -5165,7 +5188,7 @@
       </c>
       <c r="EW13">
         <f t="shared" si="56"/>
-        <v>6.8963824285714279E-2</v>
+        <v>6.8901129899999997E-2</v>
       </c>
       <c r="EY13">
         <f t="shared" si="57"/>
@@ -5221,7 +5244,7 @@
       </c>
       <c r="FL13">
         <f t="shared" si="69"/>
-        <v>1.0042480800000001E-2</v>
+        <v>1.0033351272E-2</v>
       </c>
       <c r="FN13">
         <f>Constants!$B$24</f>
@@ -5604,7 +5627,7 @@
       </c>
       <c r="EA14" s="2">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB14" s="2">
         <f t="shared" si="35"/>
@@ -5624,7 +5647,7 @@
       </c>
       <c r="EF14" s="2">
         <f t="shared" si="39"/>
-        <v>78.946371428571425</v>
+        <v>78.874601999999996</v>
       </c>
       <c r="EG14" s="2">
         <f t="shared" si="40"/>
@@ -5676,7 +5699,7 @@
       </c>
       <c r="ES14" s="2">
         <f t="shared" si="52"/>
-        <v>34.144305642857141</v>
+        <v>34.113265365000004</v>
       </c>
       <c r="ET14" s="2">
         <f t="shared" si="53"/>
@@ -5692,7 +5715,7 @@
       </c>
       <c r="EW14" s="2">
         <f t="shared" si="56"/>
-        <v>0.11309067707142856</v>
+        <v>0.11298786736499999</v>
       </c>
       <c r="EY14" s="2">
         <f t="shared" si="57"/>
@@ -5748,7 +5771,7 @@
       </c>
       <c r="FL14" s="2">
         <f t="shared" si="69"/>
-        <v>1.6468213079999999E-2</v>
+        <v>1.6453241977200002E-2</v>
       </c>
       <c r="FN14" s="2">
         <f>Constants!$B$24</f>
@@ -6206,7 +6229,7 @@
       </c>
       <c r="EA15">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB15" s="18">
         <f t="shared" si="35"/>
@@ -6214,11 +6237,11 @@
       </c>
       <c r="EC15" s="18">
         <f t="shared" si="36"/>
-        <v>0.64040625000000007</v>
+        <v>0.63982406250000012</v>
       </c>
       <c r="ED15" s="18">
         <f t="shared" si="37"/>
-        <v>2.2770000000000001</v>
+        <v>2.2749300000000003</v>
       </c>
       <c r="EE15" s="18">
         <f t="shared" si="38"/>
@@ -6226,11 +6249,11 @@
       </c>
       <c r="EF15" s="18">
         <f t="shared" si="39"/>
-        <v>1.1385000000000001</v>
+        <v>1.1374650000000002</v>
       </c>
       <c r="EG15" s="18">
         <f t="shared" si="40"/>
-        <v>8.5387500000000005E-2</v>
+        <v>8.5309875000000007E-2</v>
       </c>
       <c r="EH15">
         <f t="shared" si="41"/>
@@ -6278,7 +6301,7 @@
       </c>
       <c r="ES15">
         <f t="shared" si="52"/>
-        <v>0.29316375000000006</v>
+        <v>0.29289723750000007</v>
       </c>
       <c r="ET15">
         <f t="shared" si="53"/>
@@ -6286,7 +6309,7 @@
       </c>
       <c r="EU15">
         <f t="shared" si="54"/>
-        <v>0.15221033437500001</v>
+        <v>0.15207196134375003</v>
       </c>
       <c r="EV15">
         <f t="shared" si="55"/>
@@ -6294,11 +6317,11 @@
       </c>
       <c r="EW15" s="18">
         <f t="shared" si="56"/>
-        <v>4.5866678343749996E-3</v>
+        <v>4.5824981363437505E-3</v>
       </c>
       <c r="EX15">
         <f>SUM(EW15:EW18)</f>
-        <v>0.12445323324853573</v>
+        <v>0.12434009394558253</v>
       </c>
       <c r="EY15" s="18">
         <f t="shared" si="57"/>
@@ -6354,11 +6377,11 @@
       </c>
       <c r="FL15">
         <f t="shared" si="69"/>
-        <v>1.1998089365625002E-3</v>
+        <v>1.1987182011656253E-3</v>
       </c>
       <c r="FM15">
         <f t="shared" ref="FM15" si="90">SUM(FL15:FL18)</f>
-        <v>3.2555246385317864E-2</v>
+        <v>3.2525650706785758E-2</v>
       </c>
       <c r="FN15" s="18">
         <f>Constants!$B$24</f>
@@ -6378,11 +6401,11 @@
       </c>
       <c r="FR15" s="18">
         <f t="shared" si="9"/>
-        <v>2.5046999999999996E-2</v>
+        <v>2.5024229999999998E-2</v>
       </c>
       <c r="FS15">
         <f t="shared" ref="FS15" si="91">SUM(FR15:FR18)/1000</f>
-        <v>6.7961758857142866E-4</v>
+        <v>6.7899975440000005E-4</v>
       </c>
     </row>
     <row r="16" spans="1:175" x14ac:dyDescent="0.2">
@@ -6816,7 +6839,7 @@
       </c>
       <c r="EA16">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB16">
         <f t="shared" ref="EB16:EB26" si="117">DI16*DU16*$EA16</f>
@@ -6824,11 +6847,11 @@
       </c>
       <c r="EC16">
         <f t="shared" ref="EC16:EC26" si="118">DJ16*DV16*$EA16</f>
-        <v>6.1547062500000003</v>
+        <v>6.1491110625000012</v>
       </c>
       <c r="ED16">
         <f t="shared" ref="ED16:ED26" si="119">DK16*DW16*$EA16</f>
-        <v>21.883400000000002</v>
+        <v>21.863506000000005</v>
       </c>
       <c r="EE16">
         <f t="shared" ref="EE16:EE26" si="120">DL16*DX16*$EA16</f>
@@ -6836,11 +6859,11 @@
       </c>
       <c r="EF16">
         <f t="shared" ref="EF16:EF26" si="121">DM16*DY16*$EA16</f>
-        <v>10.941700000000001</v>
+        <v>10.931753000000002</v>
       </c>
       <c r="EG16">
         <f t="shared" ref="EG16:EG26" si="122">DN16*DZ16*$EA16</f>
-        <v>0.82062750000000018</v>
+        <v>0.81988147500000019</v>
       </c>
       <c r="EH16">
         <f t="shared" ref="EH16:EH26" si="123">DI16*(1-DO16-DU16)</f>
@@ -6888,7 +6911,7 @@
       </c>
       <c r="ES16">
         <f t="shared" ref="ES16:ES26" si="134">EN16*DV16*$EA16</f>
-        <v>2.8174877500000006</v>
+        <v>2.8149263975000007</v>
       </c>
       <c r="ET16">
         <f t="shared" ref="ET16:ET26" si="135">EO16*DX16*$EA16</f>
@@ -6896,7 +6919,7 @@
       </c>
       <c r="EU16">
         <f t="shared" ref="EU16:EU26" si="136">EP16*DZ16*$EA16</f>
-        <v>1.462836904375</v>
+        <v>1.4615070526437501</v>
       </c>
       <c r="EV16">
         <f t="shared" ref="EV16:EV26" si="137">EQ16*0*$EA16</f>
@@ -6904,7 +6927,7 @@
       </c>
       <c r="EW16">
         <f t="shared" si="56"/>
-        <v>4.4080758404375003E-2</v>
+        <v>4.4040684987643762E-2</v>
       </c>
       <c r="EY16">
         <f t="shared" ref="EY16:EY22" si="138">DI16*DO16</f>
@@ -6960,7 +6983,7 @@
       </c>
       <c r="FL16">
         <f t="shared" si="69"/>
-        <v>1.1530917383562501E-2</v>
+        <v>1.1520434731395626E-2</v>
       </c>
       <c r="FN16">
         <f>Constants!$B$24</f>
@@ -6980,7 +7003,7 @@
       </c>
       <c r="FR16">
         <f t="shared" si="9"/>
-        <v>0.2407174</v>
+        <v>0.24049856600000002</v>
       </c>
     </row>
     <row r="17" spans="1:175" x14ac:dyDescent="0.2">
@@ -7414,7 +7437,7 @@
       </c>
       <c r="EA17">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB17">
         <f t="shared" si="117"/>
@@ -7422,11 +7445,11 @@
       </c>
       <c r="EC17">
         <f t="shared" si="118"/>
-        <v>9.88218</v>
+        <v>9.8731962000000006</v>
       </c>
       <c r="ED17">
         <f t="shared" si="119"/>
-        <v>35.136640000000007</v>
+        <v>35.104697600000009</v>
       </c>
       <c r="EE17">
         <f t="shared" si="120"/>
@@ -7434,11 +7457,11 @@
       </c>
       <c r="EF17">
         <f t="shared" si="121"/>
-        <v>17.568320000000003</v>
+        <v>17.552348800000004</v>
       </c>
       <c r="EG17">
         <f t="shared" si="122"/>
-        <v>1.3176240000000004</v>
+        <v>1.3164261600000005</v>
       </c>
       <c r="EH17">
         <f t="shared" si="123"/>
@@ -7486,7 +7509,7 @@
       </c>
       <c r="ES17">
         <f t="shared" si="134"/>
-        <v>4.5238424000000013</v>
+        <v>4.5197298160000017</v>
       </c>
       <c r="ET17">
         <f t="shared" si="135"/>
@@ -7494,7 +7517,7 @@
       </c>
       <c r="EU17">
         <f t="shared" si="136"/>
-        <v>2.3487745820000003</v>
+        <v>2.3466393323800006</v>
       </c>
       <c r="EV17">
         <f t="shared" si="137"/>
@@ -7502,7 +7525,7 @@
       </c>
       <c r="EW17">
         <f t="shared" si="56"/>
-        <v>7.077738098200001E-2</v>
+        <v>7.0713037908380016E-2</v>
       </c>
       <c r="EY17">
         <f t="shared" si="138"/>
@@ -7558,7 +7581,7 @@
       </c>
       <c r="FL17">
         <f t="shared" si="69"/>
-        <v>1.8514385012200003E-2</v>
+        <v>1.8497553753098004E-2</v>
       </c>
       <c r="FN17">
         <f>Constants!$B$24</f>
@@ -7578,7 +7601,7 @@
       </c>
       <c r="FR17">
         <f t="shared" si="9"/>
-        <v>0.38650304000000002</v>
+        <v>0.38615167360000008</v>
       </c>
     </row>
     <row r="18" spans="1:175" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -8012,7 +8035,7 @@
       </c>
       <c r="EA18" s="2">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB18" s="2">
         <f t="shared" si="117"/>
@@ -8020,11 +8043,11 @@
       </c>
       <c r="EC18" s="2">
         <f t="shared" si="118"/>
-        <v>0.69929357142857151</v>
+        <v>0.69865785000000014</v>
       </c>
       <c r="ED18" s="2">
         <f t="shared" si="119"/>
-        <v>2.4863771428571435</v>
+        <v>2.4841168000000007</v>
       </c>
       <c r="EE18" s="2">
         <f t="shared" si="120"/>
@@ -8032,11 +8055,11 @@
       </c>
       <c r="EF18" s="2">
         <f t="shared" si="121"/>
-        <v>1.2431885714285718</v>
+        <v>1.2420584000000003</v>
       </c>
       <c r="EG18" s="2">
         <f t="shared" si="122"/>
-        <v>9.3239142857142868E-2</v>
+        <v>9.3154380000000023E-2</v>
       </c>
       <c r="EH18" s="2">
         <f t="shared" si="123"/>
@@ -8084,7 +8107,7 @@
       </c>
       <c r="ES18" s="2">
         <f t="shared" si="134"/>
-        <v>0.32012105714285721</v>
+        <v>0.31983003800000009</v>
       </c>
       <c r="ET18" s="2">
         <f t="shared" si="135"/>
@@ -8092,7 +8115,7 @@
       </c>
       <c r="EU18" s="2">
         <f t="shared" si="136"/>
-        <v>0.16620654207142857</v>
+        <v>0.16605544521500001</v>
       </c>
       <c r="EV18" s="2">
         <f t="shared" si="137"/>
@@ -8100,7 +8123,7 @@
       </c>
       <c r="EW18" s="2">
         <f t="shared" si="56"/>
-        <v>5.0084260277857154E-3</v>
+        <v>5.0038729132150005E-3</v>
       </c>
       <c r="EY18" s="2">
         <f t="shared" si="138"/>
@@ -8156,7 +8179,7 @@
       </c>
       <c r="FL18" s="2">
         <f t="shared" si="69"/>
-        <v>1.3101350529928573E-3</v>
+        <v>1.3089440211265001E-3</v>
       </c>
       <c r="FN18" s="2">
         <f>Constants!$B$24</f>
@@ -8176,7 +8199,7 @@
       </c>
       <c r="FR18" s="2">
         <f t="shared" si="9"/>
-        <v>2.7350148571428576E-2</v>
+        <v>2.7325284800000006E-2</v>
       </c>
     </row>
     <row r="19" spans="1:175" x14ac:dyDescent="0.2">
@@ -8557,7 +8580,7 @@
       </c>
       <c r="EA19">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB19" s="18">
         <f t="shared" si="117"/>
@@ -8581,7 +8604,7 @@
       </c>
       <c r="EG19" s="18">
         <f t="shared" si="122"/>
-        <v>5.7828571428571429</v>
+        <v>5.7776000000000005</v>
       </c>
       <c r="EH19">
         <f t="shared" si="123"/>
@@ -8629,7 +8652,7 @@
       </c>
       <c r="ES19">
         <f t="shared" si="134"/>
-        <v>5.4069714285714285</v>
+        <v>5.402056</v>
       </c>
       <c r="ET19">
         <f t="shared" si="135"/>
@@ -8637,7 +8660,7 @@
       </c>
       <c r="EU19">
         <f t="shared" si="136"/>
-        <v>0.86742857142857144</v>
+        <v>0.86664000000000008</v>
       </c>
       <c r="EV19">
         <f t="shared" si="137"/>
@@ -8645,11 +8668,11 @@
       </c>
       <c r="EW19" s="18">
         <f t="shared" si="56"/>
-        <v>1.2057257142857143E-2</v>
+        <v>1.2046296000000001E-2</v>
       </c>
       <c r="EX19">
         <f>SUM(EW19:EW22)</f>
-        <v>0.13975744451428571</v>
+        <v>0.13963039229200003</v>
       </c>
       <c r="EY19" s="18">
         <f t="shared" si="138"/>
@@ -8705,11 +8728,11 @@
       </c>
       <c r="FL19">
         <f t="shared" si="69"/>
-        <v>5.7500105142857137E-3</v>
+        <v>5.7447832319999998E-3</v>
       </c>
       <c r="FM19">
         <f t="shared" ref="FM19" si="151">SUM(FL19:FL22)</f>
-        <v>1.1087853095314286E-2</v>
+        <v>1.1077773228864E-2</v>
       </c>
       <c r="FN19" s="18">
         <f>Constants!$B$24</f>
@@ -8733,7 +8756,7 @@
       </c>
       <c r="FS19">
         <f t="shared" ref="FS19" si="152">SUM(FR19:FR22)/1000</f>
-        <v>7.992914285714285E-4</v>
+        <v>7.9856480000000004E-4</v>
       </c>
     </row>
     <row r="20" spans="1:175" x14ac:dyDescent="0.2">
@@ -9110,7 +9133,7 @@
       </c>
       <c r="EA20">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB20">
         <f t="shared" si="117"/>
@@ -9134,7 +9157,7 @@
       </c>
       <c r="EG20">
         <f t="shared" si="122"/>
-        <v>1.4352800000000003</v>
+        <v>1.4339752000000003</v>
       </c>
       <c r="EH20">
         <f t="shared" si="123"/>
@@ -9182,7 +9205,7 @@
       </c>
       <c r="ES20">
         <f t="shared" si="134"/>
-        <v>1.3419868000000001</v>
+        <v>1.3407668120000003</v>
       </c>
       <c r="ET20">
         <f t="shared" si="135"/>
@@ -9190,7 +9213,7 @@
       </c>
       <c r="EU20">
         <f t="shared" si="136"/>
-        <v>0.21529199999999998</v>
+        <v>0.21509628</v>
       </c>
       <c r="EV20">
         <f t="shared" si="137"/>
@@ -9198,7 +9221,7 @@
       </c>
       <c r="EW20">
         <f t="shared" si="56"/>
-        <v>2.9925588000000005E-3</v>
+        <v>2.9898382920000009E-3</v>
       </c>
       <c r="EY20">
         <f t="shared" si="138"/>
@@ -9254,7 +9277,7 @@
       </c>
       <c r="FL20">
         <f t="shared" si="69"/>
-        <v>1.4271276096000001E-3</v>
+        <v>1.4258302208640002E-3</v>
       </c>
       <c r="FN20">
         <f>Constants!$B$24</f>
@@ -9636,7 +9659,7 @@
       </c>
       <c r="EA21">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB21">
         <f t="shared" si="117"/>
@@ -9648,7 +9671,7 @@
       </c>
       <c r="ED21">
         <f t="shared" si="119"/>
-        <v>66.719714285714289</v>
+        <v>66.659060000000011</v>
       </c>
       <c r="EE21">
         <f t="shared" si="120"/>
@@ -9656,7 +9679,7 @@
       </c>
       <c r="EF21">
         <f t="shared" si="121"/>
-        <v>33.359857142857145</v>
+        <v>33.329530000000005</v>
       </c>
       <c r="EG21">
         <f t="shared" si="122"/>
@@ -9708,7 +9731,7 @@
       </c>
       <c r="ES21">
         <f t="shared" si="134"/>
-        <v>14.428138214285715</v>
+        <v>14.415021725000003</v>
       </c>
       <c r="ET21">
         <f t="shared" si="135"/>
@@ -9724,7 +9747,7 @@
       </c>
       <c r="EW21">
         <f t="shared" si="56"/>
-        <v>0.11450770964285714</v>
+        <v>0.11440361172500002</v>
       </c>
       <c r="EY21">
         <f t="shared" si="138"/>
@@ -9780,7 +9803,7 @@
       </c>
       <c r="FL21">
         <f t="shared" si="69"/>
-        <v>3.5908550228571428E-3</v>
+        <v>3.5875906092000002E-3</v>
       </c>
       <c r="FN21">
         <f>Constants!$B$24</f>
@@ -9800,7 +9823,7 @@
       </c>
       <c r="FR21">
         <f t="shared" si="9"/>
-        <v>0.73391685714285715</v>
+        <v>0.73324966000000003</v>
       </c>
     </row>
     <row r="22" spans="1:175" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -10166,7 +10189,7 @@
       </c>
       <c r="EA22" s="2">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB22" s="2">
         <f t="shared" si="117"/>
@@ -10178,7 +10201,7 @@
       </c>
       <c r="ED22" s="2">
         <f t="shared" si="119"/>
-        <v>5.9431428571428571</v>
+        <v>5.9377400000000007</v>
       </c>
       <c r="EE22" s="2">
         <f t="shared" si="120"/>
@@ -10186,7 +10209,7 @@
       </c>
       <c r="EF22" s="2">
         <f t="shared" si="121"/>
-        <v>2.9715714285714285</v>
+        <v>2.9688700000000003</v>
       </c>
       <c r="EG22" s="2">
         <f t="shared" si="122"/>
@@ -10238,7 +10261,7 @@
       </c>
       <c r="ES22" s="2">
         <f t="shared" si="134"/>
-        <v>1.2852046428571426</v>
+        <v>1.2840362749999998</v>
       </c>
       <c r="ET22" s="2">
         <f t="shared" si="135"/>
@@ -10254,7 +10277,7 @@
       </c>
       <c r="EW22" s="2">
         <f t="shared" si="56"/>
-        <v>1.0199918928571429E-2</v>
+        <v>1.0190646275000001E-2</v>
       </c>
       <c r="EY22" s="2">
         <f t="shared" si="138"/>
@@ -10310,7 +10333,7 @@
       </c>
       <c r="FL22" s="2">
         <f t="shared" si="69"/>
-        <v>3.1985994857142852E-4</v>
+        <v>3.1956916679999999E-4</v>
       </c>
       <c r="FN22" s="2">
         <f>Constants!$B$24</f>
@@ -10330,7 +10353,7 @@
       </c>
       <c r="FR22" s="2">
         <f t="shared" si="9"/>
-        <v>6.5374571428571421E-2</v>
+        <v>6.5315140000000008E-2</v>
       </c>
     </row>
     <row r="23" spans="1:175" x14ac:dyDescent="0.2">
@@ -10759,7 +10782,7 @@
       </c>
       <c r="EA23">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB23" s="18">
         <f t="shared" si="117"/>
@@ -10783,7 +10806,7 @@
       </c>
       <c r="EG23" s="18">
         <f t="shared" si="122"/>
-        <v>8.6742857142857144</v>
+        <v>8.6664000000000012</v>
       </c>
       <c r="EH23">
         <f t="shared" si="123"/>
@@ -10831,7 +10854,7 @@
       </c>
       <c r="ES23">
         <f t="shared" si="134"/>
-        <v>7.2289328571428584</v>
+        <v>7.2223611000000014</v>
       </c>
       <c r="ET23">
         <f t="shared" si="135"/>
@@ -10839,7 +10862,7 @@
       </c>
       <c r="EU23">
         <f t="shared" si="136"/>
-        <v>2.8299857142857143</v>
+        <v>2.827413</v>
       </c>
       <c r="EV23">
         <f t="shared" si="137"/>
@@ -10847,11 +10870,11 @@
       </c>
       <c r="EW23" s="18">
         <f t="shared" si="56"/>
-        <v>1.8733204285714285E-2</v>
+        <v>1.8716174100000003E-2</v>
       </c>
       <c r="EX23">
         <f>SUM(EW23:EW26)</f>
-        <v>0.39576377893721426</v>
+        <v>0.39540399368363499</v>
       </c>
       <c r="EY23" s="18">
         <f t="shared" ref="EY23:EY26" si="154">DI23*DO23</f>
@@ -10907,11 +10930,11 @@
       </c>
       <c r="FL23">
         <f t="shared" si="69"/>
-        <v>1.1750886792857143E-2</v>
+        <v>1.1740204168499999E-2</v>
       </c>
       <c r="FM23">
         <f t="shared" ref="FM23" si="165">SUM(FL23:FL26)</f>
-        <v>3.4612166980010711E-2</v>
+        <v>3.458070137366525E-2</v>
       </c>
       <c r="FN23" s="18">
         <f>Constants!$B$24</f>
@@ -11357,7 +11380,7 @@
       </c>
       <c r="EA24">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB24">
         <f t="shared" si="117"/>
@@ -11369,7 +11392,7 @@
       </c>
       <c r="ED24">
         <f t="shared" si="119"/>
-        <v>92.4</v>
+        <v>92.316000000000017</v>
       </c>
       <c r="EE24">
         <f t="shared" si="120"/>
@@ -11377,7 +11400,7 @@
       </c>
       <c r="EF24">
         <f t="shared" si="121"/>
-        <v>46.2</v>
+        <v>46.158000000000008</v>
       </c>
       <c r="EG24">
         <f t="shared" si="122"/>
@@ -11429,7 +11452,7 @@
       </c>
       <c r="ES24">
         <f t="shared" si="134"/>
-        <v>3.9962999999999997</v>
+        <v>3.992667</v>
       </c>
       <c r="ET24">
         <f t="shared" si="135"/>
@@ -11437,7 +11460,7 @@
       </c>
       <c r="EU24">
         <f t="shared" si="136"/>
-        <v>1.5985199999999999</v>
+        <v>1.5970667999999999</v>
       </c>
       <c r="EV24">
         <f t="shared" si="137"/>
@@ -11445,7 +11468,7 @@
       </c>
       <c r="EW24">
         <f t="shared" si="56"/>
-        <v>0.14419482000000003</v>
+        <v>0.14406373380000001</v>
       </c>
       <c r="EY24">
         <f t="shared" si="154"/>
@@ -11501,7 +11524,7 @@
       </c>
       <c r="FL24">
         <f t="shared" si="69"/>
-        <v>8.0120039999999997E-3</v>
+        <v>8.0047203599999985E-3</v>
       </c>
       <c r="FN24">
         <f>Constants!$B$24</f>
@@ -11946,7 +11969,7 @@
       </c>
       <c r="EA25">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB25">
         <f t="shared" si="117"/>
@@ -11954,7 +11977,7 @@
       </c>
       <c r="EC25">
         <f t="shared" si="118"/>
-        <v>2.7016785714285714</v>
+        <v>2.6992224999999999</v>
       </c>
       <c r="ED25">
         <f t="shared" si="119"/>
@@ -11970,7 +11993,7 @@
       </c>
       <c r="EG25">
         <f t="shared" si="122"/>
-        <v>1.2968057142857141</v>
+        <v>1.2956268</v>
       </c>
       <c r="EH25">
         <f t="shared" si="123"/>
@@ -12018,7 +12041,7 @@
       </c>
       <c r="ES25">
         <f t="shared" si="134"/>
-        <v>1.080725462142857</v>
+        <v>1.0797429844499999</v>
       </c>
       <c r="ET25">
         <f t="shared" si="135"/>
@@ -12026,7 +12049,7 @@
       </c>
       <c r="EU25">
         <f t="shared" si="136"/>
-        <v>0.68082299999999984</v>
+        <v>0.68020406999999983</v>
       </c>
       <c r="EV25">
         <f t="shared" si="137"/>
@@ -12034,7 +12057,7 @@
       </c>
       <c r="EW25">
         <f t="shared" si="56"/>
-        <v>5.7600327478571425E-3</v>
+        <v>5.7547963544499993E-3</v>
       </c>
       <c r="EY25">
         <f t="shared" si="154"/>
@@ -12090,7 +12113,7 @@
       </c>
       <c r="FL25">
         <f t="shared" si="69"/>
-        <v>2.2320990084249994E-3</v>
+        <v>2.2300698275082493E-3</v>
       </c>
       <c r="FN25">
         <f>Constants!$B$24</f>
@@ -12532,7 +12555,7 @@
       </c>
       <c r="EA26" s="2">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB26" s="2">
         <f t="shared" si="117"/>
@@ -12544,7 +12567,7 @@
       </c>
       <c r="ED26" s="2">
         <f t="shared" si="119"/>
-        <v>145.51005857142854</v>
+        <v>145.3777767</v>
       </c>
       <c r="EE26" s="2">
         <f t="shared" si="120"/>
@@ -12552,7 +12575,7 @@
       </c>
       <c r="EF26" s="2">
         <f t="shared" si="121"/>
-        <v>72.755029285714272</v>
+        <v>72.688888349999999</v>
       </c>
       <c r="EG26" s="2">
         <f t="shared" si="122"/>
@@ -12604,7 +12627,7 @@
       </c>
       <c r="ES26" s="2">
         <f t="shared" si="134"/>
-        <v>6.2933100332142855</v>
+        <v>6.2875888422750004</v>
       </c>
       <c r="ET26" s="2">
         <f t="shared" si="135"/>
@@ -12612,7 +12635,7 @@
       </c>
       <c r="EU26" s="2">
         <f t="shared" si="136"/>
-        <v>2.5173240132857146</v>
+        <v>2.5150355369100001</v>
       </c>
       <c r="EV26" s="2">
         <f t="shared" si="137"/>
@@ -12620,7 +12643,7 @@
       </c>
       <c r="EW26" s="2">
         <f t="shared" si="56"/>
-        <v>0.22707572190364281</v>
+        <v>0.22686928942918499</v>
       </c>
       <c r="EY26" s="2">
         <f t="shared" si="154"/>
@@ -12676,7 +12699,7 @@
       </c>
       <c r="FL26" s="2">
         <f t="shared" si="69"/>
-        <v>1.2617177178728572E-2</v>
+        <v>1.2605707017657002E-2</v>
       </c>
       <c r="FN26" s="2">
         <f>Constants!$B$24</f>
@@ -14282,7 +14305,7 @@
       </c>
       <c r="EA38">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB38" s="18">
         <f>DI38*DU38*$EA38</f>
@@ -14290,7 +14313,7 @@
       </c>
       <c r="EC38" s="18">
         <f t="shared" ref="EC38:EC61" si="192">DJ38*DV38*$EA38</f>
-        <v>1.0988999999999998</v>
+        <v>1.097901</v>
       </c>
       <c r="ED38" s="18">
         <f t="shared" ref="ED38:ED61" si="193">DK38*DW38*$EA38</f>
@@ -14362,7 +14385,7 @@
       </c>
       <c r="EU38">
         <f>EP38*DZ38*$EA38</f>
-        <v>0.17472509999999999</v>
+        <v>0.174566259</v>
       </c>
       <c r="EV38">
         <f>EQ38*0*$EA38</f>
@@ -14370,11 +14393,11 @@
       </c>
       <c r="EW38" s="18">
         <f>SUM(EB38:EG38,ER38:EV38)/1000</f>
-        <v>1.2736250999999998E-3</v>
+        <v>1.2724672589999998E-3</v>
       </c>
       <c r="EX38">
         <f>SUM(EW38:EW41)</f>
-        <v>0.20966435339142861</v>
+        <v>0.20947374943380004</v>
       </c>
       <c r="EY38" s="18">
         <f>DI38*DO38</f>
@@ -14430,11 +14453,11 @@
       </c>
       <c r="FL38">
         <f>(EA38*FJ38*FK38)/1000</f>
-        <v>2.4349334624999995E-3</v>
+        <v>2.4327198866250003E-3</v>
       </c>
       <c r="FM38">
         <f>SUM(FL38:FL41)</f>
-        <v>3.7193940217499999E-2</v>
+        <v>3.7160127544574997E-2</v>
       </c>
       <c r="FN38" s="18">
         <f>Constants!$B$24</f>
@@ -14853,7 +14876,7 @@
       </c>
       <c r="EA39">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB39">
         <f t="shared" ref="EB39:EB45" si="231">DI39*DU39*$EA39</f>
@@ -14861,7 +14884,7 @@
       </c>
       <c r="EC39">
         <f t="shared" si="192"/>
-        <v>2.1559371428571428</v>
+        <v>2.1539772000000004</v>
       </c>
       <c r="ED39">
         <f t="shared" si="193"/>
@@ -14933,7 +14956,7 @@
       </c>
       <c r="EU39">
         <f t="shared" ref="EU39:EU45" si="237">EP39*DZ39*$EA39</f>
-        <v>0.3427940057142857</v>
+        <v>0.34248237479999999</v>
       </c>
       <c r="EV39">
         <f t="shared" ref="EV39:EV45" si="238">EQ39*0*$EA39</f>
@@ -14941,7 +14964,7 @@
       </c>
       <c r="EW39">
         <f t="shared" ref="EW39:EW45" si="239">SUM(EB39:EG39,ER39:EV39)/1000</f>
-        <v>2.4987311485714283E-3</v>
+        <v>2.4964595748E-3</v>
       </c>
       <c r="EY39">
         <f t="shared" ref="EY39:EY45" si="240">DI39*DO39</f>
@@ -14997,7 +15020,7 @@
       </c>
       <c r="FL39">
         <f t="shared" ref="FL39:FL61" si="247">(EA39*FJ39*FK39)/1000</f>
-        <v>4.7771075549999991E-3</v>
+        <v>4.7727647299500003E-3</v>
       </c>
       <c r="FN39">
         <f>Constants!$B$24</f>
@@ -15403,7 +15426,7 @@
       </c>
       <c r="EA40">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB40">
         <f t="shared" si="231"/>
@@ -15423,7 +15446,7 @@
       </c>
       <c r="EF40">
         <f t="shared" si="195"/>
-        <v>41.862857142857145</v>
+        <v>41.824800000000003</v>
       </c>
       <c r="EG40">
         <f t="shared" si="196"/>
@@ -15475,7 +15498,7 @@
       </c>
       <c r="ES40">
         <f t="shared" si="235"/>
-        <v>18.105685714285716</v>
+        <v>18.089226000000004</v>
       </c>
       <c r="ET40">
         <f t="shared" si="236"/>
@@ -15491,7 +15514,7 @@
       </c>
       <c r="EW40">
         <f t="shared" si="239"/>
-        <v>5.9968542857142863E-2</v>
+        <v>5.9914026000000009E-2</v>
       </c>
       <c r="EY40">
         <f t="shared" si="240"/>
@@ -15547,7 +15570,7 @@
       </c>
       <c r="FL40">
         <f t="shared" si="247"/>
-        <v>8.7325920000000008E-3</v>
+        <v>8.7246532800000012E-3</v>
       </c>
       <c r="FN40">
         <f>Constants!$B$24</f>
@@ -15980,7 +16003,7 @@
       </c>
       <c r="EA41" s="2">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB41" s="2">
         <f t="shared" si="231"/>
@@ -16000,7 +16023,7 @@
       </c>
       <c r="EF41" s="2">
         <f t="shared" si="195"/>
-        <v>101.86628571428574</v>
+        <v>101.77368000000003</v>
       </c>
       <c r="EG41" s="2">
         <f t="shared" si="196"/>
@@ -16052,7 +16075,7 @@
       </c>
       <c r="ES41" s="2">
         <f t="shared" si="235"/>
-        <v>44.057168571428576</v>
+        <v>44.017116600000008</v>
       </c>
       <c r="ET41" s="2">
         <f t="shared" si="236"/>
@@ -16068,7 +16091,7 @@
       </c>
       <c r="EW41" s="2">
         <f t="shared" si="239"/>
-        <v>0.14592345428571432</v>
+        <v>0.14579079660000002</v>
       </c>
       <c r="EX41" s="2"/>
       <c r="EY41" s="2">
@@ -16125,7 +16148,7 @@
       </c>
       <c r="FL41" s="2">
         <f t="shared" si="247"/>
-        <v>2.1249307200000001E-2</v>
+        <v>2.1229989647999999E-2</v>
       </c>
       <c r="FM41" s="2"/>
       <c r="FN41" s="2">
@@ -16612,7 +16635,7 @@
       </c>
       <c r="EA42">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB42" s="18">
         <f t="shared" si="231"/>
@@ -16620,11 +16643,11 @@
       </c>
       <c r="EC42" s="18">
         <f t="shared" si="192"/>
-        <v>1.119380625</v>
+        <v>1.1183630062500001</v>
       </c>
       <c r="ED42" s="18">
         <f t="shared" si="193"/>
-        <v>3.9105000000000003</v>
+        <v>3.9069450000000003</v>
       </c>
       <c r="EE42" s="18">
         <f t="shared" si="194"/>
@@ -16632,11 +16655,11 @@
       </c>
       <c r="EF42" s="18">
         <f t="shared" si="195"/>
-        <v>1.9552500000000002</v>
+        <v>1.9534725000000002</v>
       </c>
       <c r="EG42" s="18">
         <f t="shared" si="196"/>
-        <v>0.14273324999999998</v>
+        <v>0.14260349249999998</v>
       </c>
       <c r="EH42">
         <f t="shared" si="232"/>
@@ -16684,7 +16707,7 @@
       </c>
       <c r="ES42">
         <f t="shared" si="235"/>
-        <v>0.49920465375</v>
+        <v>0.49875083133750003</v>
       </c>
       <c r="ET42">
         <f t="shared" si="236"/>
@@ -16692,7 +16715,7 @@
       </c>
       <c r="EU42">
         <f t="shared" si="237"/>
-        <v>0.26198150343749999</v>
+        <v>0.26174333843437503</v>
       </c>
       <c r="EV42">
         <f t="shared" si="238"/>
@@ -16700,11 +16723,11 @@
       </c>
       <c r="EW42" s="18">
         <f t="shared" si="239"/>
-        <v>7.8890500321875008E-3</v>
+        <v>7.8818781685218754E-3</v>
       </c>
       <c r="EX42">
         <f>SUM(EW42:EW45)</f>
-        <v>0.16271647748511964</v>
+        <v>0.16256855341467863</v>
       </c>
       <c r="EY42" s="18">
         <f t="shared" si="240"/>
@@ -16760,11 +16783,11 @@
       </c>
       <c r="FL42">
         <f t="shared" si="247"/>
-        <v>2.0614383565875001E-3</v>
+        <v>2.0595643217178748E-3</v>
       </c>
       <c r="FM42">
         <f t="shared" ref="FM42" si="250">SUM(FL42:FL45)</f>
-        <v>4.2520810684709504E-2</v>
+        <v>4.2482155402268858E-2</v>
       </c>
       <c r="FN42" s="18">
         <f>Constants!$B$24</f>
@@ -16784,11 +16807,11 @@
       </c>
       <c r="FR42" s="18">
         <f t="shared" si="211"/>
-        <v>4.3015499999999998E-2</v>
+        <v>4.2976395000000001E-2</v>
       </c>
       <c r="FS42">
         <f t="shared" ref="FS42" si="251">SUM(FR42:FR45)/1000</f>
-        <v>8.8691859142857148E-4</v>
+        <v>8.8611230180000024E-4</v>
       </c>
     </row>
     <row r="43" spans="1:175" x14ac:dyDescent="0.2">
@@ -17249,7 +17272,7 @@
       </c>
       <c r="EA43">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB43">
         <f t="shared" si="231"/>
@@ -17257,11 +17280,11 @@
       </c>
       <c r="EC43">
         <f t="shared" si="192"/>
-        <v>8.8209082500000005</v>
+        <v>8.8128892425000007</v>
       </c>
       <c r="ED43">
         <f t="shared" si="193"/>
-        <v>30.815400000000004</v>
+        <v>30.787386000000005</v>
       </c>
       <c r="EE43">
         <f t="shared" si="194"/>
@@ -17269,11 +17292,11 @@
       </c>
       <c r="EF43">
         <f t="shared" si="195"/>
-        <v>15.407700000000002</v>
+        <v>15.393693000000003</v>
       </c>
       <c r="EG43">
         <f t="shared" si="196"/>
-        <v>1.1247621000000003</v>
+        <v>1.1237395890000004</v>
       </c>
       <c r="EH43">
         <f t="shared" si="232"/>
@@ -17321,7 +17344,7 @@
       </c>
       <c r="ES43">
         <f t="shared" si="235"/>
-        <v>3.9338169255000004</v>
+        <v>3.9302407282950007</v>
       </c>
       <c r="ET43">
         <f t="shared" si="236"/>
@@ -17329,7 +17352,7 @@
       </c>
       <c r="EU43">
         <f t="shared" si="237"/>
-        <v>2.0644584633749998</v>
+        <v>2.0625816829537502</v>
       </c>
       <c r="EV43">
         <f t="shared" si="238"/>
@@ -17337,7 +17360,7 @@
       </c>
       <c r="EW43">
         <f t="shared" si="239"/>
-        <v>6.2167045738875E-2</v>
+        <v>6.2110530242748749E-2</v>
       </c>
       <c r="EY43">
         <f t="shared" si="240"/>
@@ -17393,7 +17416,7 @@
       </c>
       <c r="FL43">
         <f t="shared" si="247"/>
-        <v>1.6244482171995003E-2</v>
+        <v>1.6229714460929554E-2</v>
       </c>
       <c r="FN43">
         <f>Constants!$B$24</f>
@@ -17413,7 +17436,7 @@
       </c>
       <c r="FR43">
         <f t="shared" si="211"/>
-        <v>0.33896940000000003</v>
+        <v>0.33866124600000008</v>
       </c>
     </row>
     <row r="44" spans="1:175" x14ac:dyDescent="0.2">
@@ -17874,7 +17897,7 @@
       </c>
       <c r="EA44">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB44">
         <f t="shared" si="231"/>
@@ -17882,11 +17905,11 @@
       </c>
       <c r="EC44">
         <f t="shared" si="192"/>
-        <v>12.297824</v>
+        <v>12.28664416</v>
       </c>
       <c r="ED44">
         <f t="shared" si="193"/>
-        <v>42.775040000000004</v>
+        <v>42.736153600000002</v>
       </c>
       <c r="EE44">
         <f t="shared" si="194"/>
@@ -17894,11 +17917,11 @@
       </c>
       <c r="EF44">
         <f t="shared" si="195"/>
-        <v>21.387520000000002</v>
+        <v>21.368076800000001</v>
       </c>
       <c r="EG44">
         <f t="shared" si="196"/>
-        <v>1.5826764799999997</v>
+        <v>1.5812376831999999</v>
       </c>
       <c r="EH44">
         <f t="shared" si="232"/>
@@ -17946,7 +17969,7 @@
       </c>
       <c r="ES44">
         <f t="shared" si="235"/>
-        <v>5.4438189343999994</v>
+        <v>5.438870008096</v>
       </c>
       <c r="ET44">
         <f t="shared" si="236"/>
@@ -17954,7 +17977,7 @@
       </c>
       <c r="EU44">
         <f t="shared" si="237"/>
-        <v>2.8592440799999999</v>
+        <v>2.8566447672000002</v>
       </c>
       <c r="EV44">
         <f t="shared" si="238"/>
@@ -17962,7 +17985,7 @@
       </c>
       <c r="EW44">
         <f t="shared" si="239"/>
-        <v>8.6346123494400004E-2</v>
+        <v>8.6267627018495996E-2</v>
       </c>
       <c r="EY44">
         <f t="shared" si="240"/>
@@ -18018,7 +18041,7 @@
       </c>
       <c r="FL44">
         <f t="shared" si="247"/>
-        <v>2.2564788285423999E-2</v>
+        <v>2.2544274841528159E-2</v>
       </c>
       <c r="FN44">
         <f>Constants!$B$24</f>
@@ -18038,7 +18061,7 @@
       </c>
       <c r="FR44">
         <f t="shared" si="211"/>
-        <v>0.47052544000000002</v>
+        <v>0.47009768960000003</v>
       </c>
     </row>
     <row r="45" spans="1:175" x14ac:dyDescent="0.2">
@@ -18502,7 +18525,7 @@
       </c>
       <c r="EA45" s="2">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB45" s="2">
         <f t="shared" si="231"/>
@@ -18510,11 +18533,11 @@
       </c>
       <c r="EC45" s="2">
         <f t="shared" si="192"/>
-        <v>0.8993065714285714</v>
+        <v>0.89848901999999997</v>
       </c>
       <c r="ED45" s="2">
         <f t="shared" si="193"/>
-        <v>3.1280228571428572</v>
+        <v>3.1251792000000003</v>
       </c>
       <c r="EE45" s="2">
         <f t="shared" si="194"/>
@@ -18522,11 +18545,11 @@
       </c>
       <c r="EF45" s="2">
         <f t="shared" si="195"/>
-        <v>1.5640114285714286</v>
+        <v>1.5625896000000001</v>
       </c>
       <c r="EG45" s="2">
         <f t="shared" si="196"/>
-        <v>0.11573684571428569</v>
+        <v>0.11563163039999999</v>
       </c>
       <c r="EH45" s="2">
         <f t="shared" si="232"/>
@@ -18574,7 +18597,7 @@
       </c>
       <c r="ES45" s="2">
         <f t="shared" si="235"/>
-        <v>0.39809173894285715</v>
+        <v>0.39772983736200007</v>
       </c>
       <c r="ET45" s="2">
         <f t="shared" si="236"/>
@@ -18582,7 +18605,7 @@
       </c>
       <c r="EU45" s="2">
         <f t="shared" si="237"/>
-        <v>0.20908877785714289</v>
+        <v>0.20889869715000003</v>
       </c>
       <c r="EV45" s="2">
         <f t="shared" si="238"/>
@@ -18590,7 +18613,7 @@
       </c>
       <c r="EW45" s="2">
         <f t="shared" si="239"/>
-        <v>6.3142582196571428E-3</v>
+        <v>6.3085179849120014E-3</v>
       </c>
       <c r="EX45" s="2"/>
       <c r="EY45" s="2">
@@ -18647,7 +18670,7 @@
       </c>
       <c r="FL45" s="2">
         <f t="shared" si="247"/>
-        <v>1.6501018707030001E-3</v>
+        <v>1.6486017780932706E-3</v>
       </c>
       <c r="FM45" s="2"/>
       <c r="FN45" s="2">
@@ -18668,7 +18691,7 @@
       </c>
       <c r="FR45" s="2">
         <f t="shared" si="211"/>
-        <v>3.4408251428571429E-2</v>
+        <v>3.4376971200000002E-2</v>
       </c>
       <c r="FS45" s="2"/>
     </row>
@@ -19077,7 +19100,7 @@
       </c>
       <c r="EA46">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB46" s="18">
         <f>DI46*DU46*$EA46</f>
@@ -19101,7 +19124,7 @@
       </c>
       <c r="EG46" s="18">
         <f t="shared" si="196"/>
-        <v>5.6571428571428575</v>
+        <v>5.6520000000000001</v>
       </c>
       <c r="EH46">
         <f t="shared" si="232"/>
@@ -19149,7 +19172,7 @@
       </c>
       <c r="ES46">
         <f>EN46*DV46*$EA46</f>
-        <v>5.2894285714285711</v>
+        <v>5.2846200000000003</v>
       </c>
       <c r="ET46">
         <f>EO46*DX46*$EA46</f>
@@ -19157,7 +19180,7 @@
       </c>
       <c r="EU46">
         <f>EP46*DZ46*$EA46</f>
-        <v>0.84857142857142864</v>
+        <v>0.84780000000000011</v>
       </c>
       <c r="EV46">
         <f>EQ46*0*$EA46</f>
@@ -19165,11 +19188,11 @@
       </c>
       <c r="EW46" s="18">
         <f>SUM(EB46:EG46,ER46:EV46)/1000</f>
-        <v>1.1795142857142856E-2</v>
+        <v>1.178442E-2</v>
       </c>
       <c r="EX46">
         <f t="shared" ref="EX46" si="253">SUM(EW46:EW49)</f>
-        <v>8.1437788771428571E-2</v>
+        <v>8.1363754418000006E-2</v>
       </c>
       <c r="EY46" s="18">
         <f>DI46*DO46</f>
@@ -19225,11 +19248,11 @@
       </c>
       <c r="FL46">
         <f t="shared" si="247"/>
-        <v>5.6250102857142853E-3</v>
+        <v>5.6198966400000001E-3</v>
       </c>
       <c r="FM46">
         <f>SUM(FL46:FL49)</f>
-        <v>8.7204694669714283E-3</v>
+        <v>8.7125417674560005E-3</v>
       </c>
       <c r="FN46" s="18">
         <f>Constants!$B$24</f>
@@ -19253,7 +19276,7 @@
       </c>
       <c r="FS46">
         <f>SUM(FR46:FR49)/1000</f>
-        <v>4.3324914285714286E-4</v>
+        <v>4.3285528000000002E-4</v>
       </c>
     </row>
     <row r="47" spans="1:175" x14ac:dyDescent="0.2">
@@ -19657,7 +19680,7 @@
       </c>
       <c r="EA47">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB47">
         <f t="shared" ref="EB47:EB61" si="271">DI47*DU47*$EA47</f>
@@ -19681,7 +19704,7 @@
       </c>
       <c r="EG47">
         <f t="shared" si="196"/>
-        <v>0.98126285714285733</v>
+        <v>0.98037080000000021</v>
       </c>
       <c r="EH47">
         <f t="shared" si="232"/>
@@ -19729,7 +19752,7 @@
       </c>
       <c r="ES47">
         <f t="shared" ref="ES47:ES61" si="278">EN47*DV47*$EA47</f>
-        <v>0.91748077142857165</v>
+        <v>0.9166466980000002</v>
       </c>
       <c r="ET47">
         <f t="shared" ref="ET47:ET61" si="279">EO47*DX47*$EA47</f>
@@ -19737,7 +19760,7 @@
       </c>
       <c r="EU47">
         <f t="shared" ref="EU47:EU61" si="280">EP47*DZ47*$EA47</f>
-        <v>0.14718942857142858</v>
+        <v>0.14705562000000003</v>
       </c>
       <c r="EV47">
         <f t="shared" ref="EV47:EV61" si="281">EQ47*0*$EA47</f>
@@ -19745,7 +19768,7 @@
       </c>
       <c r="EW47">
         <f t="shared" ref="EW47:EW61" si="282">SUM(EB47:EG47,ER47:EV47)/1000</f>
-        <v>2.0459330571428575E-3</v>
+        <v>2.0440731180000004E-3</v>
       </c>
       <c r="EY47">
         <f t="shared" ref="EY47:EY61" si="283">DI47*DO47</f>
@@ -19801,7 +19824,7 @@
       </c>
       <c r="FL47">
         <f t="shared" si="247"/>
-        <v>9.7568928411428588E-4</v>
+        <v>9.7480229385600028E-4</v>
       </c>
       <c r="FN47">
         <f>Constants!$B$24</f>
@@ -20210,7 +20233,7 @@
       </c>
       <c r="EA48">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB48">
         <f t="shared" si="271"/>
@@ -20222,7 +20245,7 @@
       </c>
       <c r="ED48">
         <f t="shared" si="193"/>
-        <v>31.909428571428574</v>
+        <v>31.880420000000004</v>
       </c>
       <c r="EE48">
         <f t="shared" si="194"/>
@@ -20230,7 +20253,7 @@
       </c>
       <c r="EF48">
         <f t="shared" si="195"/>
-        <v>15.954714285714287</v>
+        <v>15.940210000000002</v>
       </c>
       <c r="EG48">
         <f t="shared" si="196"/>
@@ -20282,7 +20305,7 @@
       </c>
       <c r="ES48">
         <f t="shared" si="278"/>
-        <v>6.9004139285714281</v>
+        <v>6.894140825</v>
       </c>
       <c r="ET48">
         <f t="shared" si="279"/>
@@ -20298,7 +20321,7 @@
       </c>
       <c r="EW48">
         <f t="shared" si="282"/>
-        <v>5.4764556785714291E-2</v>
+        <v>5.4714770825000009E-2</v>
       </c>
       <c r="EY48">
         <f t="shared" si="283"/>
@@ -20354,7 +20377,7 @@
       </c>
       <c r="FL48">
         <f t="shared" si="247"/>
-        <v>1.7173654457142854E-3</v>
+        <v>1.7158042043999998E-3</v>
       </c>
       <c r="FN48">
         <f>Constants!$B$24</f>
@@ -20374,7 +20397,7 @@
       </c>
       <c r="FR48">
         <f t="shared" si="211"/>
-        <v>0.35100371428571431</v>
+        <v>0.35068462</v>
       </c>
     </row>
     <row r="49" spans="1:175" x14ac:dyDescent="0.2">
@@ -20790,7 +20813,7 @@
       </c>
       <c r="EA49" s="2">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB49" s="2">
         <f t="shared" si="271"/>
@@ -20802,7 +20825,7 @@
       </c>
       <c r="ED49" s="2">
         <f t="shared" si="193"/>
-        <v>7.4768571428571429</v>
+        <v>7.4700600000000001</v>
       </c>
       <c r="EE49" s="2">
         <f t="shared" si="194"/>
@@ -20810,7 +20833,7 @@
       </c>
       <c r="EF49" s="2">
         <f t="shared" si="195"/>
-        <v>3.7384285714285714</v>
+        <v>3.7350300000000001</v>
       </c>
       <c r="EG49" s="2">
         <f t="shared" si="196"/>
@@ -20862,7 +20885,7 @@
       </c>
       <c r="ES49" s="2">
         <f t="shared" si="278"/>
-        <v>1.6168703571428571</v>
+        <v>1.6154004749999999</v>
       </c>
       <c r="ET49" s="2">
         <f t="shared" si="279"/>
@@ -20878,7 +20901,7 @@
       </c>
       <c r="EW49" s="2">
         <f t="shared" si="282"/>
-        <v>1.283215607142857E-2</v>
+        <v>1.2820490475E-2</v>
       </c>
       <c r="EX49" s="2"/>
       <c r="EY49" s="2">
@@ -20935,7 +20958,7 @@
       </c>
       <c r="FL49" s="2">
         <f t="shared" si="247"/>
-        <v>4.0240445142857148E-4</v>
+        <v>4.0203862920000006E-4</v>
       </c>
       <c r="FM49" s="2"/>
       <c r="FN49" s="2">
@@ -20956,7 +20979,7 @@
       </c>
       <c r="FR49" s="2">
         <f t="shared" si="211"/>
-        <v>8.2245428571428567E-2</v>
+        <v>8.2170659999999993E-2</v>
       </c>
       <c r="FS49" s="2"/>
     </row>
@@ -21413,7 +21436,7 @@
       </c>
       <c r="EA50">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB50" s="18">
         <f t="shared" si="271"/>
@@ -21437,7 +21460,7 @@
       </c>
       <c r="EG50" s="18">
         <f t="shared" si="196"/>
-        <v>10.559999999999999</v>
+        <v>10.5504</v>
       </c>
       <c r="EH50">
         <f t="shared" si="232"/>
@@ -21485,7 +21508,7 @@
       </c>
       <c r="ES50">
         <f t="shared" si="278"/>
-        <v>8.80044</v>
+        <v>8.7924396000000016</v>
       </c>
       <c r="ET50">
         <f t="shared" si="279"/>
@@ -21493,7 +21516,7 @@
       </c>
       <c r="EU50">
         <f t="shared" si="280"/>
-        <v>3.4452000000000003</v>
+        <v>3.4420680000000003</v>
       </c>
       <c r="EV50">
         <f t="shared" si="281"/>
@@ -21501,11 +21524,11 @@
       </c>
       <c r="EW50" s="18">
         <f t="shared" si="282"/>
-        <v>2.2805639999999995E-2</v>
+        <v>2.2784907600000001E-2</v>
       </c>
       <c r="EX50">
         <f t="shared" ref="EX50" si="292">SUM(EW50:EW53)</f>
-        <v>0.52559808988570711</v>
+        <v>0.5251202734403565</v>
       </c>
       <c r="EY50" s="18">
         <f t="shared" si="283"/>
@@ -21561,11 +21584,11 @@
       </c>
       <c r="FL50">
         <f t="shared" si="247"/>
-        <v>1.4305427399999999E-2</v>
+        <v>1.4292422466E-2</v>
       </c>
       <c r="FM50">
         <f t="shared" ref="FM50" si="293">SUM(FL50:FL53)</f>
-        <v>4.3449249757864503E-2</v>
+        <v>4.3409750439902806E-2</v>
       </c>
       <c r="FN50" s="18">
         <f>Constants!$B$24</f>
@@ -22038,7 +22061,7 @@
       </c>
       <c r="EA51">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB51">
         <f t="shared" si="271"/>
@@ -22050,7 +22073,7 @@
       </c>
       <c r="ED51">
         <f t="shared" si="193"/>
-        <v>105.60000000000001</v>
+        <v>105.504</v>
       </c>
       <c r="EE51">
         <f t="shared" si="194"/>
@@ -22058,7 +22081,7 @@
       </c>
       <c r="EF51">
         <f t="shared" si="195"/>
-        <v>52.800000000000004</v>
+        <v>52.752000000000002</v>
       </c>
       <c r="EG51">
         <f t="shared" si="196"/>
@@ -22110,7 +22133,7 @@
       </c>
       <c r="ES51">
         <f t="shared" si="278"/>
-        <v>4.5672000000000006</v>
+        <v>4.5630480000000011</v>
       </c>
       <c r="ET51">
         <f t="shared" si="279"/>
@@ -22118,7 +22141,7 @@
       </c>
       <c r="EU51">
         <f t="shared" si="280"/>
-        <v>1.8268800000000003</v>
+        <v>1.8252192000000005</v>
       </c>
       <c r="EV51">
         <f t="shared" si="281"/>
@@ -22126,7 +22149,7 @@
       </c>
       <c r="EW51">
         <f t="shared" si="282"/>
-        <v>0.16479408000000001</v>
+        <v>0.1646442672</v>
       </c>
       <c r="EY51">
         <f t="shared" si="283"/>
@@ -22182,7 +22205,7 @@
       </c>
       <c r="FL51">
         <f t="shared" si="247"/>
-        <v>9.1565759999999996E-3</v>
+        <v>9.1482518399999997E-3</v>
       </c>
       <c r="FN51">
         <f>Constants!$B$24</f>
@@ -22654,7 +22677,7 @@
       </c>
       <c r="EA52">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB52">
         <f t="shared" si="271"/>
@@ -22662,7 +22685,7 @@
       </c>
       <c r="EC52">
         <f t="shared" si="192"/>
-        <v>4.5063998571428581</v>
+        <v>4.5023031300000014</v>
       </c>
       <c r="ED52">
         <f t="shared" si="193"/>
@@ -22678,7 +22701,7 @@
       </c>
       <c r="EG52">
         <f t="shared" si="196"/>
-        <v>0.54465840000000021</v>
+        <v>0.54416325600000026</v>
       </c>
       <c r="EH52">
         <f t="shared" si="232"/>
@@ -22726,7 +22749,7 @@
       </c>
       <c r="ES52">
         <f t="shared" si="278"/>
-        <v>0.49280886552857156</v>
+        <v>0.49236085746900016</v>
       </c>
       <c r="ET52">
         <f t="shared" si="279"/>
@@ -22734,7 +22757,7 @@
       </c>
       <c r="EU52">
         <f t="shared" si="280"/>
-        <v>0.63094785222857142</v>
+        <v>0.63037426327200008</v>
       </c>
       <c r="EV52">
         <f t="shared" si="281"/>
@@ -22742,7 +22765,7 @@
       </c>
       <c r="EW52">
         <f t="shared" si="282"/>
-        <v>6.1748149749000008E-3</v>
+        <v>6.1692015067410025E-3</v>
       </c>
       <c r="EY52">
         <f t="shared" si="283"/>
@@ -22798,7 +22821,7 @@
       </c>
       <c r="FL52">
         <f t="shared" si="247"/>
-        <v>1.5498874483030715E-3</v>
+        <v>1.5484784597137051E-3</v>
       </c>
       <c r="FN52">
         <f>Constants!$B$24</f>
@@ -23273,7 +23296,7 @@
       </c>
       <c r="EA53" s="2">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB53" s="2">
         <f t="shared" si="271"/>
@@ -23285,7 +23308,7 @@
       </c>
       <c r="ED53" s="2">
         <f t="shared" si="193"/>
-        <v>212.63244042857144</v>
+        <v>212.43913821000001</v>
       </c>
       <c r="EE53" s="2">
         <f t="shared" si="194"/>
@@ -23293,7 +23316,7 @@
       </c>
       <c r="EF53" s="2">
         <f t="shared" si="195"/>
-        <v>106.31622021428572</v>
+        <v>106.21956910500001</v>
       </c>
       <c r="EG53" s="2">
         <f t="shared" si="196"/>
@@ -23345,7 +23368,7 @@
       </c>
       <c r="ES53" s="2">
         <f t="shared" si="278"/>
-        <v>9.1963530485357161</v>
+        <v>9.1879927275825022</v>
       </c>
       <c r="ET53" s="2">
         <f t="shared" si="279"/>
@@ -23353,7 +23376,7 @@
       </c>
       <c r="EU53" s="2">
         <f t="shared" si="280"/>
-        <v>3.6785412194142864</v>
+        <v>3.675197091033001</v>
       </c>
       <c r="EV53" s="2">
         <f t="shared" si="281"/>
@@ -23361,7 +23384,7 @@
       </c>
       <c r="EW53" s="2">
         <f t="shared" si="282"/>
-        <v>0.33182355491080717</v>
+        <v>0.33152189713361552</v>
       </c>
       <c r="EX53" s="2"/>
       <c r="EY53" s="2">
@@ -23418,7 +23441,7 @@
       </c>
       <c r="FL53" s="2">
         <f t="shared" si="247"/>
-        <v>1.8437358909561427E-2</v>
+        <v>1.8420597674189101E-2</v>
       </c>
       <c r="FM53" s="2"/>
       <c r="FN53" s="2">
@@ -23905,7 +23928,7 @@
       </c>
       <c r="EA54">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB54" s="18">
         <f t="shared" si="271"/>
@@ -23913,11 +23936,11 @@
       </c>
       <c r="EC54" s="18">
         <f t="shared" si="192"/>
-        <v>0.94390312499999995</v>
+        <v>0.94304503125000005</v>
       </c>
       <c r="ED54" s="18">
         <f t="shared" si="193"/>
-        <v>3.3560999999999996</v>
+        <v>3.3530489999999999</v>
       </c>
       <c r="EE54" s="18">
         <f t="shared" si="194"/>
@@ -23925,11 +23948,11 @@
       </c>
       <c r="EF54" s="18">
         <f t="shared" si="195"/>
-        <v>1.6780499999999998</v>
+        <v>1.6765245</v>
       </c>
       <c r="EG54" s="18">
         <f t="shared" si="196"/>
-        <v>0.12585374999999999</v>
+        <v>0.12573933749999999</v>
       </c>
       <c r="EH54">
         <f t="shared" ref="EH54:EH61" si="301">DI54*(1-DO54-DU54)</f>
@@ -23977,7 +24000,7 @@
       </c>
       <c r="ES54">
         <f t="shared" si="278"/>
-        <v>0.43209787500000002</v>
+        <v>0.43170505875000004</v>
       </c>
       <c r="ET54">
         <f t="shared" si="279"/>
@@ -23985,7 +24008,7 @@
       </c>
       <c r="EU54">
         <f t="shared" si="280"/>
-        <v>0.2243447971875</v>
+        <v>0.22414084737187503</v>
       </c>
       <c r="EV54">
         <f t="shared" si="281"/>
@@ -23993,11 +24016,11 @@
       </c>
       <c r="EW54" s="18">
         <f t="shared" si="282"/>
-        <v>6.7603495471875007E-3</v>
+        <v>6.7542037748718753E-3</v>
       </c>
       <c r="EX54">
         <f t="shared" ref="EX54" si="306">SUM(EW54:EW57)</f>
-        <v>0.13594752280314465</v>
+        <v>0.13582393414605087</v>
       </c>
       <c r="EY54" s="18">
         <f t="shared" si="283"/>
@@ -24053,11 +24076,11 @@
       </c>
       <c r="FL54">
         <f>(EA54*FJ54*FK54)/1000</f>
-        <v>2.3978495474999998E-3</v>
+        <v>2.3956696842750004E-3</v>
       </c>
       <c r="FM54">
         <f t="shared" ref="FM54" si="307">SUM(FL54:FL57)</f>
-        <v>4.7967469758905708E-2</v>
+        <v>4.7923862968215797E-2</v>
       </c>
       <c r="FN54" s="18">
         <f>Constants!$B$24</f>
@@ -24077,11 +24100,11 @@
       </c>
       <c r="FR54" s="18">
         <f t="shared" si="211"/>
-        <v>3.6917099999999994E-2</v>
+        <v>3.6883539E-2</v>
       </c>
       <c r="FS54">
         <f t="shared" ref="FS54" si="308">SUM(FR54:FR57)/1000</f>
-        <v>7.3951500857142845E-4</v>
+        <v>7.3884272219999986E-4</v>
       </c>
     </row>
     <row r="55" spans="1:175" x14ac:dyDescent="0.2">
@@ -24542,7 +24565,7 @@
       </c>
       <c r="EA55">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB55">
         <f t="shared" si="271"/>
@@ -24550,11 +24573,11 @@
       </c>
       <c r="EC55">
         <f t="shared" si="192"/>
-        <v>5.9062849999999996</v>
+        <v>5.90091565</v>
       </c>
       <c r="ED55">
         <f t="shared" si="193"/>
-        <v>20.543599999999998</v>
+        <v>20.524924000000002</v>
       </c>
       <c r="EE55">
         <f t="shared" si="194"/>
@@ -24562,11 +24585,11 @@
       </c>
       <c r="EF55">
         <f t="shared" si="195"/>
-        <v>10.271799999999999</v>
+        <v>10.262462000000001</v>
       </c>
       <c r="EG55">
         <f t="shared" si="196"/>
-        <v>0.76011319999999982</v>
+        <v>0.75942218799999994</v>
       </c>
       <c r="EH55">
         <f t="shared" si="301"/>
@@ -24614,7 +24637,7 @@
       </c>
       <c r="ES55">
         <f t="shared" si="278"/>
-        <v>2.6215687959999996</v>
+        <v>2.6191855516399998</v>
       </c>
       <c r="ET55">
         <f t="shared" si="279"/>
@@ -24622,7 +24645,7 @@
       </c>
       <c r="EU55">
         <f t="shared" si="280"/>
-        <v>1.3760360075</v>
+        <v>1.374785065675</v>
       </c>
       <c r="EV55">
         <f t="shared" si="281"/>
@@ -24630,7 +24653,7 @@
       </c>
       <c r="EW55">
         <f t="shared" si="282"/>
-        <v>4.147940300349999E-2</v>
+        <v>4.1441694455315002E-2</v>
       </c>
       <c r="EY55">
         <f t="shared" si="283"/>
@@ -24686,7 +24709,7 @@
       </c>
       <c r="FL55">
         <f t="shared" si="247"/>
-        <v>1.4665706255199997E-2</v>
+        <v>1.4652373794967996E-2</v>
       </c>
       <c r="FN55">
         <f>Constants!$B$24</f>
@@ -24706,7 +24729,7 @@
       </c>
       <c r="FR55">
         <f t="shared" si="211"/>
-        <v>0.22597959999999997</v>
+        <v>0.225774164</v>
       </c>
     </row>
     <row r="56" spans="1:175" x14ac:dyDescent="0.2">
@@ -25167,7 +25190,7 @@
       </c>
       <c r="EA56">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB56">
         <f t="shared" si="271"/>
@@ -25175,11 +25198,11 @@
       </c>
       <c r="EC56">
         <f t="shared" si="192"/>
-        <v>11.667656000000001</v>
+        <v>11.657049040000002</v>
       </c>
       <c r="ED56">
         <f t="shared" si="193"/>
-        <v>39.719680000000004</v>
+        <v>39.683571200000003</v>
       </c>
       <c r="EE56">
         <f t="shared" si="194"/>
@@ -25187,11 +25210,11 @@
       </c>
       <c r="EF56">
         <f t="shared" si="195"/>
-        <v>19.859840000000002</v>
+        <v>19.841785600000001</v>
       </c>
       <c r="EG56">
         <f t="shared" si="196"/>
-        <v>1.44976832</v>
+        <v>1.4484503488</v>
       </c>
       <c r="EH56">
         <f t="shared" si="301"/>
@@ -25239,7 +25262,7 @@
       </c>
       <c r="ES56">
         <f t="shared" si="278"/>
-        <v>5.0233479295999999</v>
+        <v>5.0187812496640003</v>
       </c>
       <c r="ET56">
         <f t="shared" si="279"/>
@@ -25247,7 +25270,7 @@
       </c>
       <c r="EU56">
         <f t="shared" si="280"/>
-        <v>2.665811148</v>
+        <v>2.6633876833200003</v>
       </c>
       <c r="EV56">
         <f t="shared" si="281"/>
@@ -25255,7 +25278,7 @@
       </c>
       <c r="EW56">
         <f t="shared" si="282"/>
-        <v>8.0386103397600023E-2</v>
+        <v>8.0313025121783996E-2</v>
       </c>
       <c r="EY56">
         <f t="shared" si="283"/>
@@ -25311,7 +25334,7 @@
       </c>
       <c r="FL56">
         <f t="shared" si="247"/>
-        <v>2.8331610827519997E-2</v>
+        <v>2.83058548176768E-2</v>
       </c>
       <c r="FN56">
         <f>Constants!$B$24</f>
@@ -25331,7 +25354,7 @@
       </c>
       <c r="FR56">
         <f t="shared" si="211"/>
-        <v>0.43691647999999994</v>
+        <v>0.43651928319999994</v>
       </c>
     </row>
     <row r="57" spans="1:175" x14ac:dyDescent="0.2">
@@ -25794,7 +25817,7 @@
       </c>
       <c r="EA57" s="2">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB57" s="2">
         <f t="shared" si="271"/>
@@ -25802,11 +25825,11 @@
       </c>
       <c r="EC57" s="2">
         <f t="shared" si="192"/>
-        <v>1.0827771428571429</v>
+        <v>1.0817928000000001</v>
       </c>
       <c r="ED57" s="2">
         <f t="shared" si="193"/>
-        <v>3.6092571428571425</v>
+        <v>3.6059759999999996</v>
       </c>
       <c r="EE57" s="2">
         <f t="shared" si="194"/>
@@ -25814,11 +25837,11 @@
       </c>
       <c r="EF57" s="2">
         <f t="shared" si="195"/>
-        <v>1.8046285714285712</v>
+        <v>1.8029879999999998</v>
       </c>
       <c r="EG57" s="2">
         <f t="shared" si="196"/>
-        <v>0.12993325714285711</v>
+        <v>0.129815136</v>
       </c>
       <c r="EH57" s="2">
         <f t="shared" si="301"/>
@@ -25866,7 +25889,7 @@
       </c>
       <c r="ES57" s="2">
         <f t="shared" si="278"/>
-        <v>0.45234819771428558</v>
+        <v>0.45193697207999989</v>
       </c>
       <c r="ET57" s="2">
         <f t="shared" si="279"/>
@@ -25874,7 +25897,7 @@
       </c>
       <c r="EU57" s="2">
         <f t="shared" si="280"/>
-        <v>0.24272254285714281</v>
+        <v>0.24250188599999997</v>
       </c>
       <c r="EV57" s="2">
         <f t="shared" si="281"/>
@@ -25882,7 +25905,7 @@
       </c>
       <c r="EW57" s="2">
         <f t="shared" si="282"/>
-        <v>7.3216668548571427E-3</v>
+        <v>7.3150107940799999E-3</v>
       </c>
       <c r="EX57" s="2"/>
       <c r="EY57" s="2">
@@ -25939,7 +25962,7 @@
       </c>
       <c r="FL57" s="2">
         <f t="shared" si="247"/>
-        <v>2.5723031286857137E-3</v>
+        <v>2.5699646712959998E-3</v>
       </c>
       <c r="FM57" s="2"/>
       <c r="FN57" s="2">
@@ -25960,7 +25983,7 @@
       </c>
       <c r="FR57" s="2">
         <f t="shared" si="211"/>
-        <v>3.9701828571428566E-2</v>
+        <v>3.9665736E-2</v>
       </c>
       <c r="FS57" s="2"/>
     </row>
@@ -26427,7 +26450,7 @@
       </c>
       <c r="EA58">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB58" s="18">
         <f t="shared" si="271"/>
@@ -26435,11 +26458,11 @@
       </c>
       <c r="EC58" s="18">
         <f t="shared" si="192"/>
-        <v>0.55687500000000001</v>
+        <v>0.55636874999999997</v>
       </c>
       <c r="ED58" s="18">
         <f t="shared" si="193"/>
-        <v>1.98</v>
+        <v>1.9782000000000002</v>
       </c>
       <c r="EE58" s="18">
         <f t="shared" si="194"/>
@@ -26447,11 +26470,11 @@
       </c>
       <c r="EF58" s="18">
         <f t="shared" si="195"/>
-        <v>0.99</v>
+        <v>0.98910000000000009</v>
       </c>
       <c r="EG58" s="18">
         <f t="shared" si="196"/>
-        <v>7.425000000000001E-2</v>
+        <v>7.4182500000000012E-2</v>
       </c>
       <c r="EH58">
         <f t="shared" si="301"/>
@@ -26499,7 +26522,7 @@
       </c>
       <c r="ES58">
         <f t="shared" si="278"/>
-        <v>0.25492500000000007</v>
+        <v>0.25469325000000009</v>
       </c>
       <c r="ET58">
         <f t="shared" si="279"/>
@@ -26507,7 +26530,7 @@
       </c>
       <c r="EU58">
         <f t="shared" si="280"/>
-        <v>0.1323568125</v>
+        <v>0.13223648812500002</v>
       </c>
       <c r="EV58">
         <f t="shared" si="281"/>
@@ -26515,11 +26538,11 @@
       </c>
       <c r="EW58" s="18">
         <f t="shared" si="282"/>
-        <v>3.9884068125000003E-3</v>
+        <v>3.9847809881250005E-3</v>
       </c>
       <c r="EX58">
         <f t="shared" ref="EX58" si="311">SUM(EW58:EW61)</f>
-        <v>0.10840106536992856</v>
+        <v>0.10830251894686499</v>
       </c>
       <c r="EY58" s="18">
         <f t="shared" si="283"/>
@@ -26575,11 +26598,11 @@
       </c>
       <c r="FL58">
         <f t="shared" si="247"/>
-        <v>1.0433121187499999E-3</v>
+        <v>1.0423636531875001E-3</v>
       </c>
       <c r="FM58">
         <f t="shared" ref="FM58" si="312">SUM(FL58:FL61)</f>
-        <v>2.8207521668652858E-2</v>
+        <v>2.81818784671359E-2</v>
       </c>
       <c r="FN58" s="18">
         <f>Constants!$B$24</f>
@@ -26599,11 +26622,11 @@
       </c>
       <c r="FR58" s="18">
         <f t="shared" si="211"/>
-        <v>2.1779999999999997E-2</v>
+        <v>2.17602E-2</v>
       </c>
       <c r="FS58">
         <f t="shared" ref="FS58" si="313">SUM(FR58:FR61)/1000</f>
-        <v>5.8966411428571419E-4</v>
+        <v>5.8912805600000006E-4</v>
       </c>
     </row>
     <row r="59" spans="1:175" x14ac:dyDescent="0.2">
@@ -27065,7 +27088,7 @@
       </c>
       <c r="EA59">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB59">
         <f t="shared" si="271"/>
@@ -27073,11 +27096,11 @@
       </c>
       <c r="EC59">
         <f t="shared" si="192"/>
-        <v>5.1359000000000004</v>
+        <v>5.1312310000000005</v>
       </c>
       <c r="ED59">
         <f t="shared" si="193"/>
-        <v>17.864000000000001</v>
+        <v>17.847760000000001</v>
       </c>
       <c r="EE59">
         <f t="shared" si="194"/>
@@ -27085,11 +27108,11 @@
       </c>
       <c r="EF59">
         <f t="shared" si="195"/>
-        <v>8.9320000000000004</v>
+        <v>8.9238800000000005</v>
       </c>
       <c r="EG59">
         <f t="shared" si="196"/>
-        <v>0.660968</v>
+        <v>0.66036711999999997</v>
       </c>
       <c r="EH59">
         <f t="shared" si="301"/>
@@ -27137,7 +27160,7 @@
       </c>
       <c r="ES59">
         <f t="shared" si="278"/>
-        <v>2.27962504</v>
+        <v>2.2775526536000004</v>
       </c>
       <c r="ET59">
         <f t="shared" si="279"/>
@@ -27145,7 +27168,7 @@
       </c>
       <c r="EU59">
         <f t="shared" si="280"/>
-        <v>1.1965530500000001</v>
+        <v>1.1954652745000003</v>
       </c>
       <c r="EV59">
         <f t="shared" si="281"/>
@@ -27153,7 +27176,7 @@
       </c>
       <c r="EW59">
         <f t="shared" si="282"/>
-        <v>3.6069046089999994E-2</v>
+        <v>3.6036256048099999E-2</v>
       </c>
       <c r="EY59">
         <f t="shared" si="283"/>
@@ -27209,7 +27232,7 @@
       </c>
       <c r="FL59">
         <f t="shared" si="247"/>
-        <v>9.4051811853999995E-3</v>
+        <v>9.3966310206860006E-3</v>
       </c>
       <c r="FN59">
         <f>Constants!$B$24</f>
@@ -27229,7 +27252,7 @@
       </c>
       <c r="FR59">
         <f t="shared" si="211"/>
-        <v>0.19650399999999998</v>
+        <v>0.19632536</v>
       </c>
     </row>
     <row r="60" spans="1:175" x14ac:dyDescent="0.2">
@@ -27691,7 +27714,7 @@
       </c>
       <c r="EA60">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB60">
         <f t="shared" si="271"/>
@@ -27699,11 +27722,11 @@
       </c>
       <c r="EC60">
         <f t="shared" si="192"/>
-        <v>8.9751200000000004</v>
+        <v>8.9669608000000007</v>
       </c>
       <c r="ED60">
         <f t="shared" si="193"/>
-        <v>30.553599999999999</v>
+        <v>30.525824000000004</v>
       </c>
       <c r="EE60">
         <f t="shared" si="194"/>
@@ -27711,11 +27734,11 @@
       </c>
       <c r="EF60">
         <f t="shared" si="195"/>
-        <v>15.2768</v>
+        <v>15.262912000000002</v>
       </c>
       <c r="EG60">
         <f t="shared" si="196"/>
-        <v>1.1152063999999999</v>
+        <v>1.114192576</v>
       </c>
       <c r="EH60">
         <f t="shared" si="301"/>
@@ -27763,7 +27786,7 @@
       </c>
       <c r="ES60">
         <f t="shared" si="278"/>
-        <v>3.8641137919999999</v>
+        <v>3.8606009612800003</v>
       </c>
       <c r="ET60">
         <f t="shared" si="279"/>
@@ -27771,7 +27794,7 @@
       </c>
       <c r="EU60">
         <f t="shared" si="280"/>
-        <v>2.0506239599999998</v>
+        <v>2.0487597564</v>
       </c>
       <c r="EV60">
         <f t="shared" si="281"/>
@@ -27779,7 +27802,7 @@
       </c>
       <c r="EW60">
         <f t="shared" si="282"/>
-        <v>6.1835464152000003E-2</v>
+        <v>6.1779250093680002E-2</v>
       </c>
       <c r="EY60">
         <f t="shared" si="283"/>
@@ -27835,7 +27858,7 @@
       </c>
       <c r="FL60">
         <f t="shared" si="247"/>
-        <v>1.607274075792E-2</v>
+        <v>1.60581291754128E-2</v>
       </c>
       <c r="FN60">
         <f>Constants!$B$24</f>
@@ -27855,7 +27878,7 @@
       </c>
       <c r="FR60">
         <f t="shared" si="211"/>
-        <v>0.33608959999999999</v>
+        <v>0.33578406399999999</v>
       </c>
     </row>
     <row r="61" spans="1:175" x14ac:dyDescent="0.2">
@@ -28318,7 +28341,7 @@
       </c>
       <c r="EA61" s="2">
         <f>Constants!$B$23</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="EB61" s="2">
         <f t="shared" si="271"/>
@@ -28326,11 +28349,11 @@
       </c>
       <c r="EC61" s="2">
         <f t="shared" si="192"/>
-        <v>0.96246857142857167</v>
+        <v>0.96159360000000027</v>
       </c>
       <c r="ED61" s="2">
         <f t="shared" si="193"/>
-        <v>3.2082285714285717</v>
+        <v>3.2053120000000006</v>
       </c>
       <c r="EE61" s="2">
         <f t="shared" si="194"/>
@@ -28338,11 +28361,11 @@
       </c>
       <c r="EF61" s="2">
         <f t="shared" si="195"/>
-        <v>1.6041142857142858</v>
+        <v>1.6026560000000003</v>
       </c>
       <c r="EG61" s="2">
         <f t="shared" si="196"/>
-        <v>0.11549622857142859</v>
+        <v>0.11539123200000002</v>
       </c>
       <c r="EH61" s="2">
         <f t="shared" si="301"/>
@@ -28390,7 +28413,7 @@
       </c>
       <c r="ES61" s="2">
         <f t="shared" si="278"/>
-        <v>0.4020872868571429</v>
+        <v>0.40172175296000007</v>
       </c>
       <c r="ET61" s="2">
         <f t="shared" si="279"/>
@@ -28398,7 +28421,7 @@
       </c>
       <c r="EU61" s="2">
         <f t="shared" si="280"/>
-        <v>0.21575337142857146</v>
+        <v>0.21555723200000004</v>
       </c>
       <c r="EV61" s="2">
         <f t="shared" si="281"/>
@@ -28406,7 +28429,7 @@
       </c>
       <c r="EW61" s="2">
         <f t="shared" si="282"/>
-        <v>6.5081483154285731E-3</v>
+        <v>6.5022318169600021E-3</v>
       </c>
       <c r="EX61" s="2"/>
       <c r="EY61" s="2">
@@ -28463,7 +28486,7 @@
       </c>
       <c r="FL61" s="2">
         <f t="shared" si="247"/>
-        <v>1.6862876065828576E-3</v>
+        <v>1.6847546178496006E-3</v>
       </c>
       <c r="FM61" s="2"/>
       <c r="FN61" s="2">
@@ -28484,7 +28507,7 @@
       </c>
       <c r="FR61" s="2">
         <f t="shared" si="211"/>
-        <v>3.5290514285714288E-2</v>
+        <v>3.5258432000000006E-2</v>
       </c>
       <c r="FS61" s="2"/>
     </row>
